--- a/df_log_20260307.xlsx
+++ b/df_log_20260307.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,28 +456,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>인천시설관리공단</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -489,31 +489,7258 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>울산시설관리공단</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.uic.or.kr/notify/noti01.do</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>대구시설관리공단</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>부산시설관리공단</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>17</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>15</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>대전시설관리공단</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>세종시설관리공단</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>전남도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2016-08-12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>충북도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>경북플랫폼</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>경북도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>경북도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>충남도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>전북도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>강원도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>경남도로관리사업소</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>부산광역시고시공고</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.busan.go.kr/nbgosi?curPage=2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>광주도시관리공사</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.gumc.or.kr/news/bidding</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>광주도시관리공사</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.gumc.or.kr/news/news</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>서울특별시건설신기술공법선정위원회</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>인천광역시종합건설본부</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>울산광역시고시공고</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>대구광역시고시공고</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>세종소개공고</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>강원고시공고</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>90</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>충북고시공고</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>충남고시공고</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>전북고시공고</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>전남고시공고</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>경기고시공고</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>경북고시공고</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>경남고시공고</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>90</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>경기도_고양시</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>경기도_수원시</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>광주광역시고시공고</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>경기도감사위원회고시공고</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>경기도_수원_장안구</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>서울시설관리공단</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>경기도_수원_팔달구</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>경기도_수원_영통구</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>대전광역시고시공고</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>40</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>경기도_용인시공법선정위원회</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>경기도_광명시</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>90</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>경기도_구리시</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>경기도_군포시</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>90</v>
+      </c>
+      <c r="D45" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>경기도_김포시</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.gimpo.go.kr/portal/ntfcPblancList.do?key=1004&amp;cate_cd=1&amp;searchCnd=40900000000&amp;pageUnit=90</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>90</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>경기도_과천시</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>20</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>경기도_남양주시</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>경기도_동두천시</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>경기도_부천시</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>경기도_수원_권선구</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>20</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>경기도_성남시수정구</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>30</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>경기도_광주시</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>40</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>경기도_성남시중원구</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>경기도_안산시</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=2</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>경기도_용인시처인구</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>70</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>경기도_시흥시</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>30</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>경기도_양주시</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>23</v>
+      </c>
+      <c r="D58" t="n">
+        <v>13</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>경기도_안양시</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>경기도_여주시</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>경기도_오산시</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>경기도_성남시분당구</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>40</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>경기도_의왕시</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>경기도_의정부시</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>경기도_이천시</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>경기도_포천시</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01&amp;pageUnit=90</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>90</v>
+      </c>
+      <c r="D66" t="n">
+        <v>9</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>경기도_하남시</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>경기도_안성시</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>20</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>경기도_화성시</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>80</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>경기도_가평군</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>10</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>경기도_연천군</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>50</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>경기도_양평군</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>경기도_성남시</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>90</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>강원도_삼척시</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>10</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>강원도_동해시</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>90</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>강원도_원주시</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>40</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>강원도_강릉시</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>강원도_태백시</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>강원도_춘천시</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>강원도_속초시</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>강원도_양구군</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>경기도_파주시</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>40</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>강원도_인제군</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>20</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>강원도_영월군</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>강원도_고성군</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>10</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>강원도_철원군</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>10</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>강원도_평창군</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>강원도_홍천군</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>강원도_횡성군</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>충청도_제천시</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>강원도_양양군</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>20</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>충청도_청주시</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>10</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>강원도_화천군</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>충청도_충주시</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>90</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>강원도_정선군</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>충청도_괴산군</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>충청도_단양군</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>충청도_청주시_서원구</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>충청도_청주시_흥덕구</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>10</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>경기도_평택시</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>90</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>충청도_옥천군</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>10</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>충청도_음성군</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>충청도_보은군</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>충청도_계룡시</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>10</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>충청도_영동군</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>15</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>충청도_공주시</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>10</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>충청도_공주시</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>10</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>충청도_진천군</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>20</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>충청도_보령시</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>10</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>충청도_증평군</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>20</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>충청도_청주시_상당구</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>50</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>충청도_논산시</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>30</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>충청도_금산군</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>10</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>충청도_부여군</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>충청도_아산시</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>10</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>충청도_서산시</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>20</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>충청도_예산군</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>20</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>충청도_예산군</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>20</v>
+      </c>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>충청도_서천군</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>10</v>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>충청도_청양군</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>10</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>충청도_당진시</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>30</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>전라도_김제시</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>10</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>전라도_남원시</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a&amp;beginDateStr=&amp;endDateStr=&amp;searchType=postTtl&amp;keyword=%EC%A0%9C%EC%95%88&amp;paramString=Us7WVBAxc13kgzv1JU3ayAslPphGSM%2FmlfdB4qtWC4OBeJsElaKmGl7kvQ4Au%2B3O&amp;size=10</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>충청도_천안시</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>30</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>충청도_홍성군</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>20</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>전라도_전주시</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>전라도_고창군</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=2</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>전라도_정읍시</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>10</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>전라도_부안군</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>10</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>충청도_태안군</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>20</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>전라도_순창군</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>20</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>전라도_완주군</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>10</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>전라도_장수군</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>10</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>전라도_무주군</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>30</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>전라도_진안군</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>전라도_군산시</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>50</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>전라도_광양시</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>20</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>전라도_임실군</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>20</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>전라도_순천시</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>10</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>전라도_목포시</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=2</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>15</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>전라도_강진군</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>15</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>전라도_나주시</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>전라도_곡성군</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>10</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>전라도_구례군</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>10</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>전라도_익산시</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>50</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>전라도_여수시</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=2</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>15</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>전라도_보성군</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>15</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>전라도_무안군</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>15</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>전라도_영광군</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>전라도_완도군</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>15</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>전라도_신안군</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>15</v>
+      </c>
+      <c r="D151" t="n">
+        <v>15</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>전라도_장성군</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>10</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>전라도_영암군</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=2</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>10</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>전라도_진도군</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>10</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>전라도_함평군</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>10</v>
+      </c>
+      <c r="D155" t="n">
+        <v>9</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>전라도_해남군</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>100</v>
+      </c>
+      <c r="D156" t="n">
+        <v>38</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>전라도_장흥군</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" t="n">
+        <v>4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>전라도_고흥군</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>10</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>경상도_경주시</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=2</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>10</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>경상도_경산시</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>경상도_김천시</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>경상도_문경시</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>10</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>경상도_상주시</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>100</v>
+      </c>
+      <c r="D163" t="n">
+        <v>13</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>경상도_상주시</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>15</v>
+      </c>
+      <c r="D164" t="n">
+        <v>6</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>전라도_화순군</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>20</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>경상도_영주시</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>경상도_영천시</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>경상도_영천시</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.yc.go.kr/portal/bbs/list.do?ptIdx=568&amp;mId=0301030000</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>전라도_담양군</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>20</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>경상도_포항시</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>39</v>
+      </c>
+      <c r="D170" t="n">
+        <v>17</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-01-05(Mon)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-07(Sat)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>경상도_고령군</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023&amp;page=1</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>경상도_고령군</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=152&amp;BRD_ID=1019&amp;page=1</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>경상도_군위군</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>10</v>
+      </c>
+      <c r="D173" t="n">
+        <v>4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>경상도_안동시</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>10</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>경상도_성주군</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=2</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>경상도_봉화군</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>10</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>경상도_영덕군</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>10</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>경상도_영덕군</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>10</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>경상도_성주군</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=2</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>경상도_구미시</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>50</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>경상도_영양군</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=2</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>경상도_예천군</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=2</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>경상도_울진군</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>10</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>경상도_예천군</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=2</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>경상도_의성군</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=2</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>10</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>경상도_의성군</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>10</v>
+      </c>
+      <c r="D186" t="n">
+        <v>6</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>경상도_포항시</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>40</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>경상도_칠곡군</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>경상도_청송군</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>경상도_청송군</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>경상도_칠곡군</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>경상도_창원시</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>10</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>경상도_창원시</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>10</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>경상도_창원시_의창구</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>10</v>
+      </c>
+      <c r="D194" t="n">
+        <v>8</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>경상도_창원시_성산구</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>10</v>
+      </c>
+      <c r="D195" t="n">
+        <v>9</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>경상도_창원시_마산합포구</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>10</v>
+      </c>
+      <c r="D196" t="n">
+        <v>6</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>경상도_창원시_마산회원구</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>10</v>
+      </c>
+      <c r="D197" t="n">
+        <v>8</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>경상도_창원시_진해구</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>10</v>
+      </c>
+      <c r="D198" t="n">
+        <v>8</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>경상도_김해시</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>10</v>
+      </c>
+      <c r="D199" t="n">
+        <v>6</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>새 글</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>경상도_김해시</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>10</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>경상도_거제시</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>90</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>경상도_밀양시</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>10</v>
+      </c>
+      <c r="D202" t="n">
+        <v>6</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>[일자리ㆍ기업] 밀양시종합사회복지관 관장 채용 공고 새글 사회복지법인 '나눔과 베품'에서는 지역사회 복지 증진을 위해 헌신하며, 전문성과 사명감을 갖춘밀양시종합사회복지관 관장을 공개 모집합니다- ○ 접 2026-03-06 노인장애인과 조회수 : 53</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>경상도_사천시</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>10</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>경상도_양산시</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>10</v>
+      </c>
+      <c r="D204" t="n">
+        <v>7</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>경상도_밀양시</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=2</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>10</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>경상도_통영시</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>10</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>경상도_남해군_남해읍</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>10</v>
+      </c>
+      <c r="D207" t="n">
+        <v>8</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>경상도_양산시</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>20</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>경상도_남해군_이동면</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>10</v>
+      </c>
+      <c r="D209" t="n">
+        <v>9</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>경상도_의령군</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>10</v>
+      </c>
+      <c r="D210" t="n">
+        <v>3</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>경상도_남해군_상주면</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>10</v>
+      </c>
+      <c r="D211" t="n">
+        <v>10</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>경상도_청도군</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>경상도_산청군</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>90</v>
+      </c>
+      <c r="D213" t="n">
+        <v>10</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-02-20-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-03-06-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>경상도_하동군</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=2</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>10</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>경상도_남해군_삼동면</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>10</v>
+      </c>
+      <c r="D215" t="n">
+        <v>9</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>경상도_남해군_미조면</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>10</v>
+      </c>
+      <c r="D216" t="n">
+        <v>10</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>경상도_함안군</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>10</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>경상도_남해군_남면</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>10</v>
+      </c>
+      <c r="D218" t="n">
+        <v>9</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>경상도_남해군_서면</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>10</v>
+      </c>
+      <c r="D219" t="n">
+        <v>8</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>전라도_함평군</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>경상도_남해군_고현면</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>10</v>
+      </c>
+      <c r="D221" t="n">
+        <v>9</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>경상도_고성군</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>경상도_남해군_설천면</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>10</v>
+      </c>
+      <c r="D223" t="n">
+        <v>10</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>경상도_거창군</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=2</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>10</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>경상도_남해군_창선면</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>10</v>
+      </c>
+      <c r="D225" t="n">
+        <v>9</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>경상도_울릉군</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>경상도_함양군</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>30</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>경상도_진주시</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>경상도_창녕군</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>경상도_합천군</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>66</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>등록일</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
         <is>
           <t>성공</t>
         </is>

--- a/df_log_20260307.xlsx
+++ b/df_log_20260307.xlsx
@@ -489,23 +489,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>울산시설관리공단</t>
+          <t>대전시설관리공단</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.uic.or.kr/notify/noti01.do</t>
+          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -522,21 +522,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>울산시설관리공단</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
+          <t>https://www.uic.or.kr/notify/noti01.do</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -551,23 +555,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>세종시설관리공단</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -584,23 +588,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대전시설관리공단</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -617,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>세종시설관리공단</t>
+          <t>전남도로관리사업소</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
+          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -650,28 +654,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전남도로관리사업소</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -683,12 +687,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>경북플랫폼</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -699,12 +703,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -716,28 +720,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경북플랫폼</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -815,28 +819,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>경남도로관리사업소</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -848,28 +852,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -881,23 +885,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -907,63 +911,63 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경남도로관리사업소</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=2</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -980,23 +984,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=2</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1006,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1046,28 +1050,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>서울특별시건설신기술공법선정위원회</t>
+          <t>인천광역시종합건설본부</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1079,56 +1083,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인천광역시종합건설본부</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>서울특별시건설신기술공법선정위원회</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=2</t>
+          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1145,23 +1141,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=2</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1171,7 +1167,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1266,30 +1262,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>충남고시공고</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1299,7 +1295,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1332,30 +1328,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>충남고시공고</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경북고시공고</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1471,16 +1467,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>경북고시공고</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
@@ -1497,30 +1493,30 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>광주광역시고시공고</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=2</t>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1537,23 +1533,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>광주광역시고시공고</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1563,36 +1559,40 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기도감사위원회고시공고</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>경기도감사위원회고시공고</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1650,7 +1650,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -1690,23 +1690,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기도_수원_영통구</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1716,35 +1716,35 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>경기도_용인시공법선정위원회</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1756,28 +1756,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기도_용인시공법선정위원회</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1789,23 +1789,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기도_광명시</t>
+          <t>경기도_수원_영통구</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1822,23 +1822,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경기도_구리시</t>
+          <t>경기도_광명시</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1855,23 +1855,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1888,23 +1888,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기도_김포시</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.gimpo.go.kr/portal/ntfcPblancList.do?key=1004&amp;cate_cd=1&amp;searchCnd=40900000000&amp;pageUnit=90</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>90</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1921,23 +1921,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>경기도_김포시</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.gimpo.go.kr/portal/ntfcPblancList.do?key=1004&amp;cate_cd=1&amp;searchCnd=40900000000&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기도_남양주시</t>
+          <t>경기도_구리시</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
+          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -2013,55 +2013,63 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>경기도_남양주시</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>경기도_성남시수정구</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2071,30 +2079,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기도_성남시수정구</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2104,23 +2112,23 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D53" t="n">
         <v>3</v>
@@ -2144,23 +2152,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2170,7 +2178,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -2203,19 +2211,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2243,16 +2251,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>경기도_성남시분당구</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D57" t="n">
         <v>3</v>
@@ -2309,16 +2317,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
@@ -2342,28 +2350,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경기도_여주시</t>
+          <t>경기도_오산시</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=2</t>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2375,28 +2383,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경기도_오산시</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D61" t="n">
         <v>3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2408,25 +2416,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기도_성남시분당구</t>
+          <t>경기도_의왕시</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D62" t="n">
         <v>3</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -2441,21 +2445,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기도_의왕시</t>
+          <t>경기도_여주시</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -2463,55 +2471,63 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기도_의정부시</t>
+          <t>경기도_이천시</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경기도_이천시</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2587,35 +2603,35 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>경기도_화성시</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2627,56 +2643,56 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경기도_화성시</t>
+          <t>경기도_가평군</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경기도_가평군</t>
+          <t>경기도_의정부시</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=2</t>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2686,7 +2702,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -2752,30 +2768,30 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>강원도_동해시</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2818,30 +2834,30 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>강원도_동해시</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2858,12 +2874,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2917,30 +2933,30 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원도_태백시</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2957,23 +2973,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>강원도_태백시</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=2</t>
+          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2983,7 +2999,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -3023,48 +3039,56 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=2</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>강원도_영월군</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3074,7 +3098,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -3114,89 +3138,81 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원도_영월군</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원도_고성군</t>
+          <t>강원도_철원군</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>10</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원도_철원군</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3213,23 +3229,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>강원도_고성군</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3246,23 +3262,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3279,23 +3295,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3305,30 +3321,30 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3338,35 +3354,35 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>경기도_평택시</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3378,28 +3394,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>충청도_충주시</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=2</t>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3444,23 +3460,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>충청도_충주시</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3470,63 +3486,63 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3543,25 +3559,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
@@ -3634,23 +3658,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경기도_평택시</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3693,30 +3717,30 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>충청도_음성군</t>
+          <t>충청도_영동군</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=2</t>
+          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3733,33 +3757,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>충청도_음성군</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -3792,30 +3816,30 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>충청도_영동군</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3837,18 +3861,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>10</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3865,61 +3889,53 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
         <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3957,35 +3973,35 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D110" t="n">
         <v>3</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -3997,16 +4013,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D111" t="n">
         <v>3</v>
@@ -4030,16 +4046,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>충청도_서산시</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D112" t="n">
         <v>3</v>
@@ -4063,28 +4079,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4129,28 +4145,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>10</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4162,23 +4178,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>충청도_서산시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4200,7 +4216,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -4228,28 +4244,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>충청도_서천군</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4261,28 +4277,28 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>충청도_서천군</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4327,12 +4343,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>충청도_천안시</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -4411,23 +4427,23 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>충청도_천안시</t>
+          <t>충청도_홍성군</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D124" t="n">
         <v>3</v>
@@ -4451,28 +4467,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>충청도_홍성군</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D125" t="n">
         <v>3</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4484,25 +4500,33 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -4535,40 +4559,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전라도_정읍시</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -4608,23 +4624,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>전라도_정읍시</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4707,28 +4723,28 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전라도_장수군</t>
+          <t>전라도_군산시</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D133" t="n">
         <v>3</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4740,28 +4756,28 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전라도_무주군</t>
+          <t>전라도_장수군</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D134" t="n">
         <v>3</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4773,41 +4789,49 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>전라도_군산시</t>
+          <t>전라도_무주군</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D136" t="n">
         <v>3</v>
@@ -4831,33 +4855,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -4897,16 +4913,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=2</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=2</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -4923,23 +4939,23 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=2</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -4956,7 +4972,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -4996,44 +5012,52 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>전라도_나주시</t>
+          <t>전라도_곡성군</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>전라도_곡성군</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5042,7 +5066,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5054,52 +5078,52 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>전라도_구례군</t>
+          <t>전라도_여수시</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=2</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>전라도_구례군</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5108,35 +5132,35 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>전라도_여수시</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=2</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C146" t="n">
         <v>15</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5186,61 +5210,53 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>전라도_나주시</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>전라도_신안군</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5252,23 +5268,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>전라도_완도군</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5278,35 +5294,35 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>전라도_신안군</t>
+          <t>전라도_완도군</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>15</v>
       </c>
       <c r="D151" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5318,56 +5334,48 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>전라도_장성군</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>전라도_진도군</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=2</t>
+          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>10</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5384,23 +5392,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>전라도_진도군</t>
+          <t>전라도_장성군</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
+          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5410,7 +5418,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -5450,23 +5458,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>전라도_해남군</t>
+          <t>전라도_고흥군</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5476,7 +5484,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -5516,23 +5524,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>전라도_고흥군</t>
+          <t>전라도_해남군</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5549,12 +5557,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>경상도_경주시</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=2</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=2</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -5575,32 +5583,40 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>경상도_경주시</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=2</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5641,7 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -5665,33 +5681,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>13</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -5731,23 +5739,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5782,32 +5790,40 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
@@ -5832,68 +5848,60 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D170" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-01-05(Mon)</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-07(Sat)</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -5905,25 +5913,33 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023&amp;page=1</t>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-01-05(Mon)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-07(Sat)</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5951,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=152&amp;BRD_ID=1019&amp;page=1</t>
+          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023&amp;page=1</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5948,68 +5964,60 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=152&amp;BRD_ID=1019&amp;page=1</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>10</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6021,81 +6029,81 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=2</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=2</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6105,7 +6113,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -6145,95 +6153,103 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=2</t>
+          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=2</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>경상도_영양군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=2</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_영양군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=2</t>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=2</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -6246,98 +6262,90 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>경상도_울진군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=2</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_울진군</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=2</t>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=2</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=2</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -6377,23 +6385,23 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=2</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6403,7 +6411,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6436,7 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -6453,44 +6461,52 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -6503,68 +6519,60 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=2</t>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_창원시_의창구</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>10</v>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6576,28 +6584,28 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>경상도_창원시_의창구</t>
+          <t>경상도_창원시_성산구</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
         </is>
       </c>
       <c r="C194" t="n">
         <v>10</v>
       </c>
       <c r="D194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6609,28 +6617,28 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>경상도_창원시_성산구</t>
+          <t>경상도_창원시_마산합포구</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>10</v>
       </c>
       <c r="D195" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6642,28 +6650,28 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산합포구</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C196" t="n">
         <v>10</v>
       </c>
       <c r="D196" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6675,12 +6683,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>경상도_창원시_진해구</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -6691,7 +6699,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -6708,23 +6716,23 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>경상도_창원시_진해구</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>10</v>
       </c>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -6734,35 +6742,35 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_거제시</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D199" t="n">
         <v>6</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>새 글</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -6779,14 +6787,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=2</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
         </is>
       </c>
       <c r="C200" t="n">
         <v>10</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6795,7 +6803,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>새 글</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -6807,96 +6815,88 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>경상도_거제시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D201" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C202" t="n">
         <v>10</v>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>[일자리ㆍ기업] 밀양시종합사회복지관 관장 채용 공고 새글 사회복지법인 '나눔과 베품'에서는 지역사회 복지 증진을 위해 헌신하며, 전문성과 사명감을 갖춘밀양시종합사회복지관 관장을 공개 모집합니다- ○ 접 2026-03-06 노인장애인과 조회수 : 53</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>2</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6939,30 +6939,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_청도군</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=2</t>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6972,28 +6964,28 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=2</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7005,61 +6997,61 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>경상도_남해군_남해읍</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C207" t="n">
         <v>10</v>
       </c>
       <c r="D207" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20-</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06-</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7071,19 +7063,19 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>경상도_남해군_남해읍</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>10</v>
       </c>
       <c r="D209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7092,7 +7084,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7104,28 +7096,28 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>10</v>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7170,53 +7162,61 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>경상도_청도군</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
-      </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D213" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-02-20-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-06-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7254,35 +7254,35 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_남해군_미조면</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C215" t="n">
         <v>10</v>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7294,28 +7294,28 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>경상도_남해군_미조면</t>
+          <t>경상도_함안군</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C216" t="n">
         <v>10</v>
       </c>
       <c r="D216" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7327,28 +7327,28 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>경상도_함안군</t>
+          <t>경상도_남해군_남면</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>10</v>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7360,91 +7360,83 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>경상도_남해군_남면</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>9</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>경상도_남해군_서면</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>8</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>경상도_함양군</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
@@ -7484,25 +7476,33 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>경상도_남해군_서면</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
@@ -7608,12 +7608,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>경상도_울릉군</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -7626,52 +7626,44 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>경상도_함양군</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>3</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경상도_울릉군</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -7684,19 +7676,19 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경상도_합천군</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -7709,40 +7701,32 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>경상도_합천군</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>2</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>등록일</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패(Claude분석중)</t>
         </is>
       </c>
     </row>

--- a/df_log_20260307.xlsx
+++ b/df_log_20260307.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>error_msg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>auto_fixed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,6 +495,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +530,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +565,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,6 +600,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +635,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,32 +670,30 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -683,16 +701,18 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경북플랫폼</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -703,12 +723,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -716,32 +736,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>경북플랫폼</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -749,6 +771,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -782,32 +806,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>경남도로관리사업소</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -815,32 +841,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경남도로관리사업소</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -848,32 +876,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -881,27 +911,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,42 +943,46 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -956,23 +992,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>https://www.gumc.or.kr/news/news</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -980,27 +1016,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=2</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1010,35 +1048,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>서울특별시건설신기술공법선정위원회</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/news</t>
+          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1046,6 +1086,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1079,52 +1121,68 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>서울특별시건설신기술공법선정위원회</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1137,27 +1195,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>광주광역시고시공고</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=2</t>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,9 +1227,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1199,6 +1261,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1232,56 +1296,60 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>충북고시공고</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=2</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>충북고시공고</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1290,14 +1358,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1311,14 +1381,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1328,30 +1398,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>충남고시공고</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=2</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1361,30 +1433,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>경기고시공고</t>
+          <t>경북고시공고</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=2</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1394,23 +1468,25 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>충남고시공고</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -1430,6 +1506,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1463,23 +1541,25 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경북고시공고</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1488,28 +1568,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>광주광역시고시공고</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
@@ -1529,60 +1611,60 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>경기도감사위원회고시공고</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=2</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1592,30 +1674,36 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 1/2)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경기도_수원_장안구</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=4</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1625,19 +1713,25 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기도감사위원회고시공고</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1650,9 +1744,15 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1666,85 +1766,85 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>경기도_용인시공법선정위원회</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기도_용인시공법선정위원회</t>
+          <t>경기고시공고</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=6</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1752,27 +1852,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>경기도_광명시</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1785,27 +1887,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기도_수원_영통구</t>
+          <t>경기도_수원_장안구</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1816,29 +1920,35 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>성공</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경기도_광명시</t>
+          <t>경기도_구리시</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
+          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1851,27 +1961,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1884,27 +1996,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1917,6 +2031,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1950,23 +2066,25 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기도_구리시</t>
+          <t>경기도_남양주시</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1975,14 +2093,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1996,14 +2116,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2013,56 +2133,64 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기도_남양주시</t>
+          <t>경기도_수원_영통구</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_성남시수정구</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
@@ -2079,30 +2207,36 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>경기도_성남시수정구</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2112,30 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2145,30 +2281,36 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(타임아웃 (재시도 2/2))</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 2/2)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2178,30 +2320,36 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경기도_안산시</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=2</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2211,23 +2359,29 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>경기도_안산시</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D56" t="n">
         <v>3</v>
@@ -2247,16 +2401,18 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경기도_성남시분당구</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2280,6 +2436,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2305,7 +2463,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2313,27 +2471,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>경기도_성남시분당구</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2344,6 +2504,12 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>성공</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2379,20 +2545,22 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D61" t="n">
         <v>3</v>
@@ -2412,25 +2580,31 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기도_의왕시</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -2441,6 +2615,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2450,18 +2626,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=2</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2471,32 +2647,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기도_이천시</t>
+          <t>경기도_의왕시</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -2507,27 +2681,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>경기도_이천시</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2540,32 +2716,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경기도_포천시</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01&amp;pageUnit=90</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2573,6 +2751,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2586,14 +2766,14 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2603,9 +2783,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2639,27 +2821,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경기도_가평군</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=2</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2669,30 +2853,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경기도_의정부시</t>
+          <t>경기도_양평군</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2702,9 +2888,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2738,23 +2926,25 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경기도_양평군</t>
+          <t>경기도_포천시</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=2</t>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2763,12 +2953,18 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2804,6 +3000,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2817,14 +3015,14 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2834,52 +3032,52 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>경기도_의정부시</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2903,20 +3101,22 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강원도_강릉시</t>
+          <t>경기도_가평군</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D77" t="n">
         <v>2</v>
@@ -2933,35 +3133,41 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>경기도_평택시</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2969,6 +3175,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,14 +3190,14 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2999,9 +3207,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3035,27 +3245,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>강원도_강릉시</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=2</t>
+          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3065,9 +3277,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3081,14 +3295,14 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3098,9 +3312,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3134,31 +3350,43 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>강원도_고성군</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3172,14 +3400,14 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3189,23 +3417,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D86" t="n">
         <v>3</v>
@@ -3225,27 +3455,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원도_고성군</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3258,60 +3490,60 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3321,30 +3553,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3354,35 +3588,37 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경기도_평택시</t>
+          <t>강원도_화천군</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3390,27 +3626,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>충청도_충주시</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3423,27 +3661,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>강원도_화천군</t>
+          <t>충청도_충주시</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3456,27 +3696,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3486,68 +3728,72 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=2</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=9</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D96" t="n">
         <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3555,27 +3801,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>충청도_청주시_서원구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3588,27 +3836,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>충청도_청주시_서원구</t>
+          <t>충청도_청주시_흥덕구</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3621,16 +3871,18 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>충청도_청주시_흥덕구</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -3641,12 +3893,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3654,32 +3906,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D100" t="n">
         <v>3</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3687,6 +3941,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3700,14 +3956,14 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3717,9 +3973,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3753,6 +4011,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3762,18 +4022,18 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=2</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3783,30 +4043,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>충청도_계룡시</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3816,30 +4078,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>충청도_계룡시</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3852,6 +4116,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3861,18 +4127,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>10</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3885,64 +4151,74 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: form &gt; table:nth-child)</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>테이블 없음: form &gt; table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table &gt; tbody</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3952,18 +4228,18 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=3</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3973,23 +4249,25 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D110" t="n">
         <v>3</v>
@@ -4009,20 +4287,22 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D111" t="n">
         <v>3</v>
@@ -4042,6 +4322,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4075,32 +4357,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4108,6 +4392,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4141,32 +4427,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4174,6 +4462,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4207,6 +4497,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4240,6 +4532,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4273,32 +4567,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>충청도_청양군</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D119" t="n">
         <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4306,32 +4602,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>충청도_청양군</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D120" t="n">
         <v>3</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4339,6 +4637,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4372,6 +4672,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4405,31 +4707,43 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>전라도_남원시</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a&amp;beginDateStr=&amp;endDateStr=&amp;searchType=postTtl&amp;keyword=%EC%A0%9C%EC%95%88&amp;paramString=Us7WVBAxc13kgzv1JU3ayAslPphGSM%2FmlfdB4qtWC4OBeJsElaKmGl7kvQ4Au%2B3O&amp;size=10</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4463,49 +4777,53 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>전라도_남원시</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>https://namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -4526,9 +4844,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4538,18 +4862,18 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=2</t>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4559,19 +4883,21 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -4584,9 +4910,15 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4620,6 +4952,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4633,14 +4967,14 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4650,30 +4984,36 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>전라도_순창군</t>
+          <t>전라도_군산시</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4683,9 +5023,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: table:nth-child(24) &gt; )</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(24) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4719,20 +5065,22 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전라도_군산시</t>
+          <t>전라도_순창군</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D133" t="n">
         <v>3</v>
@@ -4752,56 +5100,56 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전라도_장수군</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>전라도_장수군</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4810,14 +5158,16 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4851,85 +5201,95 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>전라도_임실군</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>전라도_임실군</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=2</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4939,30 +5299,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>전라도_강진군</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=2</t>
+          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4972,35 +5334,37 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>전라도_강진군</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D141" t="n">
         <v>3</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5008,6 +5372,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5041,89 +5407,91 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>전라도_구례군</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>20</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>전라도_여수시</t>
+          <t>전라도_나주시</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=2</t>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>전라도_구례군</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5132,28 +5500,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D146" t="n">
         <v>3</v>
@@ -5173,6 +5543,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5206,57 +5578,69 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>전라도_나주시</t>
+          <t>전라도_고흥군</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>전라도_신안군</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D149" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5264,27 +5648,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>전라도_완도군</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5294,35 +5680,37 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>전라도_완도군</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D151" t="n">
         <v>3</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5330,31 +5718,43 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>전라도_신안군</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5388,6 +5788,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5401,14 +5803,14 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5418,9 +5820,11 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5454,27 +5858,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>전라도_고흥군</t>
+          <t>전라도_해남군</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5484,30 +5890,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>전라도_장흥군</t>
+          <t>전라도_여수시</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5520,27 +5928,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>전라도_해남군</t>
+          <t>전라도_장흥군</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D158" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5553,27 +5963,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>경상도_경주시</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=2</t>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5583,30 +5995,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>경상도_경주시</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=2</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5616,34 +6030,46 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>경상도_김천시</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5677,31 +6103,43 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5735,37 +6173,37 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>경상도_김천시</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>13</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>성공</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -5790,23 +6228,29 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D167" t="n">
         <v>3</v>
@@ -5826,16 +6270,18 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/bbs/list.do?ptIdx=568&amp;mId=0301030000</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -5848,60 +6294,76 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 1/2)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05(Mon)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-07(Sat)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -5909,49 +6371,49 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>17</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2026-01-05(Mon)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-03-07(Sat)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>성공</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023&amp;page=1</t>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5964,55 +6426,71 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>http://www.goryeong.go.kr/kor/boardList.do?IDX=152&amp;BRD_ID=1019&amp;page=1</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6025,49 +6503,45 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>3</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=2</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -6080,30 +6554,40 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6113,9 +6597,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6149,39 +6635,35 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=9</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6191,7 +6673,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=2</t>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=9</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -6204,30 +6686,32 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6240,41 +6724,53 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>경상도_영양군</t>
+          <t>경상도_울진군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=2</t>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_영양군</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=2</t>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=9</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -6287,67 +6783,77 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>경상도_울진군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?BRD_ID=1023&amp;IDX=154</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>성공</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=2</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6357,18 +6863,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D186" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6381,49 +6887,49 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=2</t>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: div.list1f1t3i1)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>테이블 없음: div.list1f1t3i1</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -6436,19 +6942,25 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: div.list1table4)</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>테이블 없음: div.list1table4</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=9</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -6461,52 +6973,52 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=2</t>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=9</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -6519,9 +7031,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6544,9 +7058,15 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6580,6 +7100,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6613,6 +7135,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6646,27 +7170,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -6679,16 +7205,18 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>경상도_창원시_진해구</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -6699,7 +7227,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -6712,27 +7240,29 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_창원시_진해구</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>10</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -6742,9 +7272,11 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6778,39 +7310,35 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_청도군</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>새 글</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6820,14 +7348,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=2</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>10</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6836,98 +7364,112 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>새 글</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C202" t="n">
         <v>10</v>
       </c>
       <c r="D202" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>[일자리ㆍ기업] 밀양시종합사회복지관 관장 채용 공고 새글 사회복지법인 '나눔과 베품'에서는 지역사회 복지 증진을 위해 헌신하며, 전문성과 사명감을 갖춘밀양시종합사회복지관 관장을 공개 모집합니다- ○ 접 2026-03-06 노인장애인과 조회수 : 53</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D204" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -6935,57 +7477,69 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>경상도_청도군</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
-      </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=9</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D206" t="n">
         <v>3</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -6993,65 +7547,69 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>경상도_남해군_남해읍</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=2</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C207" t="n">
         <v>10</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D208" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-02-20-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-06-</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7059,23 +7617,25 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>경상도_남해군_남해읍</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>10</v>
       </c>
       <c r="D209" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7084,7 +7644,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7092,32 +7652,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>10</v>
       </c>
       <c r="D210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7125,6 +7687,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7158,20 +7722,22 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D212" t="n">
         <v>3</v>
@@ -7191,32 +7757,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D213" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7224,39 +7792,43 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>경상도_하동군</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.hadong.go.kr/media/00012.web?cpage=2</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>10</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7290,6 +7862,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7323,6 +7897,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7356,82 +7932,104 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-02-20-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-03-06-</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_하동군</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=1</t>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>경상도_함양군</t>
+          <t>경상도_남해군_서면</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7439,6 +8037,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7472,32 +8072,34 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>경상도_남해군_서면</t>
+          <t>경상도_함양군</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D222" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7505,6 +8107,8 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7538,39 +8142,39 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>경상도_거창군</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=2</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7604,41 +8208,53 @@
           <t>성공</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>경상도_거창군</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경상도_울릉군</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -7651,19 +8267,25 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경상도_울릉군</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -7676,19 +8298,25 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>경상도_합천군</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -7701,32 +8329,52 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
-        </is>
-      </c>
+          <t>실패(최종 실패 (재시도 소진))</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>최종 실패 (재시도 소진)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경상도_합천군</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>등록일</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>실패(Claude분석중)</t>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/df_log_20260307.xlsx
+++ b/df_log_20260307.xlsx
@@ -466,33 +466,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>인천시설관리공단</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -501,33 +493,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대전시설관리공단</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -536,33 +520,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>울산시설관리공단</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.uic.or.kr/notify/noti01.do</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -571,33 +547,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>세종시설관리공단</t>
+          <t>경북플랫폼</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -606,33 +574,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -641,28 +601,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전남도로관리사업소</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -676,24 +636,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>전남도로관리사업소</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
+          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2016-08-12</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -707,28 +671,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>울산시설관리공단</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://www.uic.or.kr/notify/noti01.do</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -742,28 +706,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경북플랫폼</t>
+          <t>세종시설관리공단</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -777,12 +741,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>인천시설관리공단</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
+          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -793,12 +757,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -847,28 +811,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>인천광역시종합건설본부</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -882,28 +846,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>강원고시공고</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -917,23 +881,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -952,23 +916,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>경남고시공고</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -987,28 +951,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/news</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1022,23 +986,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1057,23 +1021,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>서울특별시건설신기술공법선정위원회</t>
+          <t>대전시설관리공단</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
+          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1092,28 +1056,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인천광역시종합건설본부</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1127,62 +1091,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>전북고시공고</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=4</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>경기도_김포시</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.gimpo.go.kr/portal/ntfcPblancList.do?key=1004&amp;cate_cd=1&amp;searchCnd=40900000000&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1201,16 +1161,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>광주광역시고시공고</t>
+          <t>경북고시공고</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
@@ -1236,21 +1196,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>세종소개공고</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -1267,28 +1231,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>강원고시공고</t>
+          <t>충북고시공고</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1302,33 +1266,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>경기도_양주시</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
+          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1337,28 +1293,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>충북고시공고</t>
+          <t>경기도_광명시</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
+          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1372,12 +1328,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>전북고시공고</t>
+          <t>경기도_구리시</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1388,12 +1344,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1407,12 +1363,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>경기도_오산시</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1423,12 +1379,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1442,12 +1398,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>경북고시공고</t>
+          <t>경기도_남양주시</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1458,12 +1414,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1477,16 +1433,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>충남고시공고</t>
+          <t>경기도_동두천시</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -1512,23 +1468,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경남고시공고</t>
+          <t>경기도_하남시</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
+          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1547,28 +1503,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1582,19 +1538,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>경기도_화성시</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1603,7 +1559,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1617,24 +1573,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기도감사위원회고시공고</t>
+          <t>경기도_안산시</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1648,16 +1608,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>충남고시공고</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
@@ -1677,33 +1637,29 @@
           <t>성공</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>타임아웃 (재시도 1/2)</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>경기도_연천군</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=4</t>
+          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1713,43 +1669,47 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=4</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>최종 실패 (재시도 소진)</t>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -1757,59 +1717,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경기도_수원_팔달구</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기도_용인시공법선정위원회</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1823,16 +1787,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기고시공고</t>
+          <t>강원도_삼척시</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=6</t>
+          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
@@ -1858,23 +1822,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기도_광명시</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1893,23 +1857,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기도_수원_장안구</t>
+          <t>강원도_태백시</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
+          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1923,32 +1887,28 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경기도_구리시</t>
+          <t>강원도_인제군</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.guri.go.kr/www/selectGosiNttList.do?key=387&amp;searchGosiSe=01,04,06&amp;pageIndex=2</t>
+          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>20</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1967,23 +1927,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경기도_양평군</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2002,12 +1962,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>강원도_철원군</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2037,23 +1997,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경기도_김포시</t>
+          <t>강원도_영월군</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.gimpo.go.kr/portal/ntfcPblancList.do?key=1004&amp;cate_cd=1&amp;searchCnd=40900000000&amp;pageUnit=90</t>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2072,28 +2032,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기도_남양주시</t>
+          <t>경기도_여주시</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.nyj.go.kr/www/selectEminwonWebList.do?key=2492&amp;cpn=2</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D48" t="n">
         <v>3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2107,23 +2067,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기도_동두천시</t>
+          <t>충청도_충주시</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2142,19 +2102,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기도_수원_영통구</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2172,32 +2132,28 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=4</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2207,12 +2163,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>테이블 없음: tbody</t>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2220,23 +2176,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기도_성남시수정구</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2255,23 +2211,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>20</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,29 +2237,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>실패(타임아웃 (재시도 2/2))</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>타임아웃 (재시도 2/2)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -2324,32 +2276,28 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>충청도_계룡시</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2363,25 +2311,21 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경기도_안산시</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D56" t="n">
         <v>3</v>
@@ -2407,23 +2351,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=3</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2433,37 +2377,41 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경기도_양주시</t>
+          <t>충청도_옥천군</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
+          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2477,28 +2425,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기도_성남시분당구</t>
+          <t>충청도_보령시</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2507,42 +2455,30 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경기도_오산시</t>
+          <t>전라도_남원시</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2551,63 +2487,59 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>충청도_부여군</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2621,23 +2553,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기도_여주시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2656,21 +2588,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기도_의왕시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -2687,28 +2623,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경기도_이천시</t>
+          <t>전라도_부안군</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>10</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2722,28 +2658,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2757,28 +2693,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경기도_하남시</t>
+          <t>전라도_김제시</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2792,19 +2728,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경기도_화성시</t>
+          <t>전라도_강진군</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
+          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2813,7 +2749,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2827,28 +2763,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2862,16 +2798,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경기도_양평군</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
@@ -2897,63 +2833,67 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경기도_연천군</t>
+          <t>경기도_포천시</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경기도_포천시</t>
+          <t>전라도_보성군</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
+          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2962,32 +2902,28 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>강원도_동해시</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3006,23 +2942,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>강원도_삼척시</t>
+          <t>전라도_곡성군</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3041,43 +2977,47 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경기도_의정부시</t>
+          <t>전라도_진도군</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>전라도_고창군</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3107,23 +3047,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경기도_가평군</t>
+          <t>전라도_완도군</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3133,41 +3073,37 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경기도_평택시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3181,12 +3117,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원도_태백시</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -3216,28 +3152,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원도_속초시</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
+          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3251,16 +3187,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원도_강릉시</t>
+          <t>충청도_음성군</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
@@ -3286,28 +3222,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원도_영월군</t>
+          <t>전라도_구례군</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>20</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3321,23 +3257,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원도_인제군</t>
+          <t>전라도_해남군</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3356,28 +3292,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원도_고성군</t>
+          <t>전라도_신안군</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3391,23 +3323,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원도_철원군</t>
+          <t>전라도_장성군</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
+          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>20</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3426,23 +3358,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3461,23 +3393,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3496,12 +3428,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>경상도_영주시</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3527,23 +3459,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>경기도_가평군</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=4</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3553,21 +3485,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>충청도_서산시</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -3597,47 +3533,43 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원도_화천군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>충청도_홍성군</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -3648,12 +3580,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3667,33 +3599,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>충청도_충주시</t>
+          <t>경상도_울진군</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -3702,23 +3626,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3737,98 +3661,90 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.yc.go.kr/portal/bbs/list.do?ptIdx=568&amp;mId=0301030000</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=9</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>충청도_청주시_서원구</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3842,16 +3758,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>충청도_청주시_흥덕구</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
+          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D98" t="n">
         <v>3</v>
@@ -3877,28 +3793,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>경상도_창원시_의창구</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3912,58 +3828,54 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>충청도_옥천군</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>20</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3973,37 +3885,41 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>충청도_영동군</t>
+          <t>경상도_창원시_성산구</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4017,28 +3933,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>충청도_음성군</t>
+          <t>경상도_창원시_마산합포구</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4052,23 +3968,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4087,23 +4003,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>충청도_계룡시</t>
+          <t>경상도_창원시_진해구</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4122,23 +4038,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4157,47 +4073,43 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -4210,12 +4122,12 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: form &gt; table:nth-child)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>테이블 없음: form &gt; table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table &gt; tbody</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4223,25 +4135,21 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>충청도_보령시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=3</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -4258,28 +4166,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>경상도_거제시</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4293,28 +4201,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D111" t="n">
         <v>3</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4328,16 +4236,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>충청도_서산시</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D112" t="n">
         <v>3</v>
@@ -4363,28 +4271,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4398,28 +4306,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>충청도_부여군</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D114" t="n">
         <v>7</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4433,68 +4341,56 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>경상도_남해군_상주면</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -4503,12 +4399,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -4519,12 +4415,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4538,19 +4434,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>충청도_서천군</t>
+          <t>경상도_남해군_남해읍</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4559,7 +4455,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4573,12 +4469,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>충청도_청양군</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -4608,28 +4504,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4643,16 +4539,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>충청도_천안시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D121" t="n">
         <v>3</v>
@@ -4678,28 +4574,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>전라도_김제시</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4713,33 +4609,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>경상도_남해군_서면</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -4748,137 +4636,129 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>충청도_홍성군</t>
+          <t>경상도_김천시</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>전라도_남원시</t>
+          <t>경상도_함안군</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
+          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>경상도_남해군_미조면</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>10</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전라도_고창군</t>
+          <t>경상도_남해군_남면</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4892,59 +4772,63 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>경상도_남해군_고현면</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>전라도_부안군</t>
+          <t>경상도_남해군_설천면</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4958,23 +4842,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>전라도_정읍시</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4984,80 +4868,72 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>전라도_군산시</t>
+          <t>경상도_남해군_창선면</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(24) &gt; )</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(24) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>전라도_완주군</t>
+          <t>경상도_하동군</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D132" t="n">
         <v>3</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5071,16 +4947,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전라도_순창군</t>
+          <t>경상도_거창군</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D133" t="n">
         <v>3</v>
@@ -5106,148 +4982,148 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전라도_장수군</t>
+          <t>경상도_경주시</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=2</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>10</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>전라도_무주군</t>
+          <t>경상도_문경시</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전라도_임실군</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>경상도_울릉군</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -5260,12 +5136,12 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -5273,100 +5149,84 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
+          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전라도_강진군</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>성공</t>
@@ -5378,82 +5238,74 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>전라도_곡성군</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>전라도_구례군</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=2</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>전라도_나주시</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -5466,46 +5318,34 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>스킵(fail)</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.gumc.or.kr/news/news</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -5514,33 +5354,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>서울특별시건설신기술공법선정위원회</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
+          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -5549,25 +5381,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>전라도_보성군</t>
+          <t>세종소개공고</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
+          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
         <v>3</v>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -5584,51 +5412,47 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>전라도_고흥군</t>
+          <t>경기도감사위원회고시공고</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>광주광역시고시공고</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D149" t="n">
         <v>3</v>
@@ -5654,16 +5478,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>전라도_완도군</t>
+          <t>경기도_수원_영통구</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
         <v>3</v>
@@ -5689,28 +5513,24 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>경기도_용인시공법선정위원회</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5724,28 +5544,28 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>전라도_신안군</t>
+          <t>경기도_수원_팔달구</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D152" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5759,23 +5579,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>전라도_진도군</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5785,32 +5605,36 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>실패(타임아웃 (재시도 2/2))</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 2/2)</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>전라도_장성군</t>
+          <t>경기도_수원_장안구</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5820,37 +5644,41 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
+          <t>실패(타임아웃 (재시도 2/2))</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 2/2)</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D155" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5864,23 +5692,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>전라도_해남군</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5899,23 +5727,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>전라도_여수시</t>
+          <t>경기고시공고</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5934,23 +5762,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>전라도_장흥군</t>
+          <t>경기도_성남시수정구</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5969,23 +5797,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>경상도_경주시</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=3</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5998,22 +5826,28 @@
           <t>성공</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Message: unknown error: net::ERR_CONNECTION_CLOSED
+  (Session info: chrome=145.0.7632.116)
+Stacktrac</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D160" t="n">
         <v>3</v>
@@ -6039,16 +5873,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
         <v>3</v>
@@ -6074,28 +5908,28 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>경상도_문경시</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6109,23 +5943,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>경기도_성남시분당구</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6144,23 +5978,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>경기도_이천시</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6179,85 +6013,97 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>경상도_김천시</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>실패(타임아웃 (재시도 2/2))</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 2/2)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>경상도_영주시</t>
+          <t>경기도_의정부시</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>강원도_동해시</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6276,12 +6122,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>경기도_의왕시</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -6294,32 +6140,36 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32))</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32)</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경기도_평택시</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6332,38 +6182,34 @@
           <t>성공</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>타임아웃 (재시도 1/2)</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>강원도_강릉시</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D170" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-01-05(Mon)</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-07(Sat)</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6377,85 +6223,93 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>강원도_속초시</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
+          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>강원도_고성군</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6474,57 +6328,61 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6536,68 +6394,60 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>강원도_화천군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>충청도_청주시_서원구</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -6606,23 +6456,23 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D178" t="n">
         <v>3</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6635,28 +6485,40 @@
           <t>성공</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 1/2)</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>충청도_청주시_흥덕구</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=9</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6668,22 +6530,30 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=9</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6695,54 +6565,50 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>경상도_울진군</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C182" t="n">
         <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6751,7 +6617,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6765,22 +6631,30 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>경상도_영양군</t>
+          <t>충청도_영동군</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=9</t>
+          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>성공</t>
@@ -6792,54 +6666,58 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?BRD_ID=1023&amp;IDX=154</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D185" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6858,16 +6736,16 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D186" t="n">
         <v>3</v>
@@ -6893,74 +6771,82 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: div.list1f1t3i1)</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>테이블 없음: div.list1f1t3i1</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>충청도_서천군</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
-      </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: div.list1table4)</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>테이블 없음: div.list1table4</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>충청도_청양군</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=9</t>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -6973,62 +6859,78 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=9</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7040,59 +6942,63 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>충청도_천안시</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>경상도_창원시_의창구</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7106,28 +7012,28 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>경상도_창원시_성산구</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D194" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7141,30 +7047,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산합포구</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7176,12 +7074,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>전라도_순창군</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -7211,28 +7109,28 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>전라도_완주군</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>10</v>
       </c>
       <c r="D197" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7246,28 +7144,28 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>경상도_창원시_진해구</t>
+          <t>전라도_장수군</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>10</v>
       </c>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7281,23 +7179,23 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>경상도_거제시</t>
+          <t>전라도_정읍시</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D199" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7316,22 +7214,30 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>경상도_청도군</t>
+          <t>전라도_임실군</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7343,63 +7249,59 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=1</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>6</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>새 글</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>전라도_나주시</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>[일자리ㆍ기업] 밀양시종합사회복지관 관장 채용 공고 새글 사회복지법인 '나눔과 베품'에서는 지역사회 복지 증진을 위해 헌신하며, 전문성과 사명감을 갖춘밀양시종합사회복지관 관장을 공개 모집합니다- ○ 접 2026-03-06 노인장애인과 조회수 : 53</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7413,63 +7315,59 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>전라도_군산시</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D204" t="n">
         <v>3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7483,23 +7381,23 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D205" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7518,16 +7416,16 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=9</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D206" t="n">
         <v>3</v>
@@ -7553,28 +7451,28 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>경상도_남해군_남해읍</t>
+          <t>전라도_무주군</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D207" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7582,29 +7480,33 @@
           <t>성공</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>타임아웃 (재시도 1/2)</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>전라도_장흥군</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7623,28 +7525,28 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>10</v>
       </c>
       <c r="D209" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7658,16 +7560,16 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>전라도_고흥군</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D210" t="n">
         <v>3</v>
@@ -7693,28 +7595,28 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>경상도_남해군_상주면</t>
+          <t>전라도_여수시</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D211" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7728,28 +7630,28 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7763,12 +7665,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -7779,12 +7681,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7798,30 +7700,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>9</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7833,30 +7727,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>경상도_남해군_미조면</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>10</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7868,30 +7754,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>경상도_함안군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>3</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7903,30 +7781,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>경상도_남해군_남면</t>
+          <t>경상도_영양군</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=5</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>9</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7938,28 +7808,28 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D218" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-02-20-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-03-06-</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7973,30 +7843,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>경상도_하동군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=5</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>성공</t>
@@ -8008,33 +7870,25 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>경상도_남해군_서면</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>8</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -8043,33 +7897,25 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>경상도_남해군_고현면</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>9</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -8078,23 +7924,23 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>경상도_함양군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8113,28 +7959,28 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>경상도_남해군_설천면</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D223" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8148,12 +7994,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>경상도_청도군</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000</t>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -8166,41 +8012,37 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>경상도_남해군_창선면</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C225" t="n">
+        <v>90</v>
+      </c>
+      <c r="D225" t="n">
         <v>10</v>
       </c>
-      <c r="D225" t="n">
-        <v>9</v>
-      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -8214,16 +8056,16 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>경상도_거창군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D226" t="n">
         <v>3</v>
@@ -8249,43 +8091,47 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>경상도_울릉군</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=5</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -8298,25 +8144,21 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>최종 실패 (재시도 소진)</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경상도_합천군</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -8329,12 +8171,12 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>실패(최종 실패 (재시도 소진))</t>
+          <t>실패(테이블 없음: table[width='639'] tr:)</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>최종 실패 (재시도 소진)</t>
+          <t>테이블 없음: table[width='639'] tr:has(td[width='300'])</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -8342,28 +8184,28 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>경상도_합천군</t>
+          <t>경상도_함양군</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>등록일</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -8372,11 +8214,7 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
